--- a/CASP/CASP16/target_list.xlsx
+++ b/CASP/CASP16/target_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tonystark/Documents/Personal Document/NUS/projects/DMFold/benchmark/casp16/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tonystark/Documents/Personal Document/NUS/projects/DMFold/benchmark/Protein-Multimers-Benchmark/CASP/CASP16/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1392B5FB-E53A-F142-93AD-884E3CEDC158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BF8C47-6CE8-8144-8F4C-D79B70ED7A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29280" yWindow="2560" windowWidth="10140" windowHeight="17440" xr2:uid="{ACF5C0FC-2B78-1543-9A9B-D98C36ED03AD}"/>
+    <workbookView xWindow="24280" yWindow="2100" windowWidth="15820" windowHeight="12480" xr2:uid="{ACF5C0FC-2B78-1543-9A9B-D98C36ED03AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Target_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,25 +54,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T2201o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Uniprot_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Q9GZX9</t>
-  </si>
-  <si>
-    <t>PDB_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H2202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A2B2</t>
   </si>
   <si>
@@ -80,73 +61,99 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Q9GZX9_plus_P43026</t>
-  </si>
-  <si>
-    <t>H2204</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A2B2C2</t>
   </si>
   <si>
-    <t>A2B2C2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T2206o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H2232</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H2233</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T2234o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A3</t>
   </si>
   <si>
     <t>A6</t>
   </si>
   <si>
-    <t>T2235o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H2236</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A3B6</t>
   </si>
   <si>
-    <t>T2237o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A4</t>
   </si>
   <si>
-    <t>T2240o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T2259o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H2272</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A1B1C1D1E1F1G1H1I1</t>
+  </si>
+  <si>
+    <t>T1201o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1204</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1206o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A1B1C1D1E1</t>
+  </si>
+  <si>
+    <t>H1213</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1B1C1</t>
+  </si>
+  <si>
+    <t>H1223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1232</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1234o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1235o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1237o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1240o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1272</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1298o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -548,10 +555,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A6220E6-AF9B-0C45-92F9-8FA79A07134C}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,16 +568,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>210</v>
@@ -578,143 +579,183 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1">
         <v>429</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>237</v>
       </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
-        <v>462</v>
+        <v>1373</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1">
-        <v>658</v>
+        <v>485</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>115</v>
+        <v>483</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1">
+        <v>658</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1">
+        <v>413</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1">
+        <v>115</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1">
+        <v>528</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1">
         <v>488</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1">
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1">
         <v>653</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="1">
-        <v>243</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="1">
         <v>6879</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1">
+        <v>342</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
